--- a/5/search/FY3_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY3_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,265 +492,265 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>117.3</v>
+        <v>128</v>
       </c>
       <c r="C2" t="n">
-        <v>27.4</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
-        <v>6224.198701743094</v>
+        <v>6085.775274158803</v>
       </c>
       <c r="F2" t="n">
-        <v>206.1908088160799</v>
+        <v>70.80227340396868</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6229.108162365205</v>
+        <v>6091.49362576939</v>
       </c>
       <c r="I2" t="n">
-        <v>276.3993666733664</v>
+        <v>275.5224249642334</v>
       </c>
       <c r="J2" t="n">
-        <v>698.236</v>
+        <v>687.456</v>
       </c>
       <c r="K2" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>116.3</v>
+        <v>118.6</v>
       </c>
       <c r="C3" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>6225.532445521081</v>
+        <v>5867.650760353615</v>
       </c>
       <c r="F3" t="n">
-        <v>225.2642334570478</v>
+        <v>-85.44342440140235</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6228.777516679658</v>
+        <v>5851.510609177226</v>
       </c>
       <c r="I3" t="n">
-        <v>271.6709130751346</v>
+        <v>269.9903043301339</v>
       </c>
       <c r="J3" t="n">
-        <v>699.216</v>
+        <v>655.9</v>
       </c>
       <c r="K3" t="n">
         <v>2.900000000000002</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="B4" t="n">
-        <v>116.3</v>
+        <v>125</v>
       </c>
       <c r="C4" t="n">
-        <v>28.2</v>
+        <v>24.6</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
-        <v>6228.777516679658</v>
+        <v>6085.859039074974</v>
       </c>
       <c r="F4" t="n">
-        <v>271.6709130751346</v>
+        <v>73.80110374908963</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6228.777516679658</v>
+        <v>6091.443366819688</v>
       </c>
       <c r="I4" t="n">
-        <v>271.6709130751346</v>
+        <v>273.7231267571607</v>
       </c>
       <c r="J4" t="n">
-        <v>700</v>
+        <v>687.456</v>
       </c>
       <c r="K4" t="n">
-        <v>2.899999999999999</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86</v>
+        <v>86.8</v>
       </c>
       <c r="B5" t="n">
-        <v>128.5</v>
+        <v>118.8</v>
       </c>
       <c r="C5" t="n">
-        <v>24.6</v>
+        <v>26.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
-        <v>6220.507189152554</v>
+        <v>6173.747783581523</v>
       </c>
       <c r="F5" t="n">
-        <v>153.3997192763304</v>
+        <v>107.7067849622667</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6229.470896028674</v>
+        <v>6183.032016291985</v>
       </c>
       <c r="I5" t="n">
-        <v>281.5866997347179</v>
+        <v>273.7674528610137</v>
       </c>
       <c r="J5" t="n">
-        <v>695.1</v>
+        <v>690.3960000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2.899999999999999</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="B6" t="n">
-        <v>116.3</v>
+        <v>113.6</v>
       </c>
       <c r="C6" t="n">
-        <v>27.4</v>
+        <v>25.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>6222.287374362504</v>
+        <v>5867.046525351733</v>
       </c>
       <c r="F6" t="n">
-        <v>178.8575538389605</v>
+        <v>-72.13713641178992</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>6228.777516679657</v>
+        <v>5851.586818997283</v>
       </c>
       <c r="I6" t="n">
-        <v>271.6709130751346</v>
+        <v>268.3120337728857</v>
       </c>
       <c r="J6" t="n">
-        <v>696.864</v>
+        <v>655.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.899999999999999</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95</v>
+        <v>86.8</v>
       </c>
       <c r="B7" t="n">
-        <v>117.1</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>5748.933938096531</v>
+        <v>6182.904743260601</v>
       </c>
       <c r="F7" t="n">
-        <v>-130.3017809950325</v>
+        <v>271.4910079186793</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>5714.233750678978</v>
+        <v>6182.904743260601</v>
       </c>
       <c r="I7" t="n">
-        <v>266.3231761032149</v>
+        <v>271.4910079186793</v>
       </c>
       <c r="J7" t="n">
-        <v>643.356</v>
+        <v>700</v>
       </c>
       <c r="K7" t="n">
-        <v>2.899999999999999</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="B8" t="n">
-        <v>119.9</v>
+        <v>123.4</v>
       </c>
       <c r="C8" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="n">
-        <v>5672.013048610546</v>
+        <v>5948.312953095341</v>
       </c>
       <c r="F8" t="n">
-        <v>-165.2916086273963</v>
+        <v>-38.8510660248312</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>5622.401576971805</v>
+        <v>5942.928885709439</v>
       </c>
       <c r="I8" t="n">
-        <v>263.487811916359</v>
+        <v>269.6019479309155</v>
       </c>
       <c r="J8" t="n">
-        <v>636.496</v>
+        <v>669.375</v>
       </c>
       <c r="K8" t="n">
-        <v>2.800000000000004</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L8" t="n">
         <v>7</v>
@@ -758,37 +758,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89.2</v>
+        <v>90</v>
       </c>
       <c r="B9" t="n">
-        <v>127.5</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="E9" t="n">
-        <v>6043.080307436433</v>
+        <v>6000</v>
       </c>
       <c r="F9" t="n">
-        <v>85.19923783070817</v>
+        <v>-28.20000000000027</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>6045.57255662697</v>
+        <v>6000</v>
       </c>
       <c r="I9" t="n">
-        <v>263.6818383663688</v>
+        <v>276.5999999999996</v>
       </c>
       <c r="J9" t="n">
-        <v>690.3960000000001</v>
+        <v>671.7760000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2.800000000000004</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="B10" t="n">
-        <v>125.5</v>
+        <v>131</v>
       </c>
       <c r="C10" t="n">
-        <v>24.6</v>
+        <v>23.4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
-        <v>6043.105439361044</v>
+        <v>6085.590991343228</v>
       </c>
       <c r="F10" t="n">
-        <v>86.99906237392543</v>
+        <v>64.20484664470177</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>6045.558594446632</v>
+        <v>6091.443366819688</v>
       </c>
       <c r="I10" t="n">
-        <v>262.68193584236</v>
+        <v>273.7231267571602</v>
       </c>
       <c r="J10" t="n">
-        <v>690.3960000000001</v>
+        <v>687.456</v>
       </c>
       <c r="K10" t="n">
-        <v>2.800000000000001</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -834,40 +834,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>117.3</v>
+        <v>121.4</v>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>6132.624382925748</v>
+        <v>5867.830397786607</v>
       </c>
       <c r="F11" t="n">
-        <v>164.3219152060942</v>
+        <v>-89.39934785777359</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>6136.553994271696</v>
+        <v>5851.309197509933</v>
       </c>
       <c r="I11" t="n">
-        <v>258.0796015825712</v>
+        <v>274.4257336600047</v>
       </c>
       <c r="J11" t="n">
-        <v>696.864</v>
+        <v>655.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.800000000000001</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY3_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY3_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,75 +492,75 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="B2" t="n">
-        <v>128</v>
+        <v>126.8</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E2" t="n">
-        <v>6085.775274158803</v>
+        <v>6042.489707208088</v>
       </c>
       <c r="F2" t="n">
-        <v>70.80227340396868</v>
+        <v>42.9033610651145</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6091.49362576939</v>
+        <v>6045.676435248694</v>
       </c>
       <c r="I2" t="n">
-        <v>275.5224249642334</v>
+        <v>271.1211131449982</v>
       </c>
       <c r="J2" t="n">
-        <v>687.456</v>
+        <v>684.124</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="B3" t="n">
-        <v>118.6</v>
+        <v>129.4</v>
       </c>
       <c r="C3" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
-        <v>5867.650760353615</v>
+        <v>6174.803926455993</v>
       </c>
       <c r="F3" t="n">
-        <v>-85.44342440140235</v>
+        <v>126.5972842205897</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>5851.510609177226</v>
+        <v>6183.471889751331</v>
       </c>
       <c r="I3" t="n">
-        <v>269.9903043301339</v>
+        <v>281.6351660827676</v>
       </c>
       <c r="J3" t="n">
-        <v>655.9</v>
+        <v>692.944</v>
       </c>
       <c r="K3" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>6</v>
@@ -568,113 +568,113 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="B4" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C4" t="n">
-        <v>24.6</v>
+        <v>23.4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6085.859039074974</v>
+        <v>6042.146237571744</v>
       </c>
       <c r="F4" t="n">
-        <v>73.80110374908963</v>
+        <v>18.3057589744858</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6091.443366819688</v>
+        <v>6045.748480099243</v>
       </c>
       <c r="I4" t="n">
-        <v>273.7231267571607</v>
+        <v>276.2806101688863</v>
       </c>
       <c r="J4" t="n">
-        <v>687.456</v>
+        <v>680.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86.8</v>
+        <v>100.6</v>
       </c>
       <c r="B5" t="n">
-        <v>118.8</v>
+        <v>138.8</v>
       </c>
       <c r="C5" t="n">
-        <v>26.2</v>
+        <v>19.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="E5" t="n">
-        <v>6173.747783581523</v>
+        <v>5499.564029685107</v>
       </c>
       <c r="F5" t="n">
-        <v>107.7067849622667</v>
+        <v>-325.94404134562</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6183.032016291985</v>
+        <v>5387.221260838906</v>
       </c>
       <c r="I5" t="n">
-        <v>273.7674528610137</v>
+        <v>274.3542350869957</v>
       </c>
       <c r="J5" t="n">
-        <v>690.3960000000001</v>
+        <v>605.1360000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="B6" t="n">
-        <v>113.6</v>
+        <v>130.2</v>
       </c>
       <c r="C6" t="n">
-        <v>25.8</v>
+        <v>23.4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
-        <v>5867.046525351733</v>
+        <v>6085.068298266322</v>
       </c>
       <c r="F6" t="n">
-        <v>-72.13713641178992</v>
+        <v>45.49214529114624</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>5851.586818997283</v>
+        <v>6091.612013517578</v>
       </c>
       <c r="I6" t="n">
-        <v>268.3120337728857</v>
+        <v>279.7607718520038</v>
       </c>
       <c r="J6" t="n">
-        <v>655.9</v>
+        <v>684.124</v>
       </c>
       <c r="K6" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>6</v>
@@ -682,192 +682,192 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86.8</v>
+        <v>89.2</v>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>6182.904743260601</v>
+        <v>6042.235595525915</v>
       </c>
       <c r="F7" t="n">
-        <v>271.4910079186793</v>
+        <v>24.70513512814523</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6182.904743260601</v>
+        <v>6045.726140610701</v>
       </c>
       <c r="I7" t="n">
-        <v>271.4910079186793</v>
+        <v>274.6807661304713</v>
       </c>
       <c r="J7" t="n">
-        <v>700</v>
+        <v>680.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>123.4</v>
+        <v>137.6</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>20.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="E8" t="n">
-        <v>5948.312953095341</v>
+        <v>5642.010063400732</v>
       </c>
       <c r="F8" t="n">
-        <v>-38.8510660248312</v>
+        <v>-243.6301707329526</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>5942.928885709439</v>
+        <v>5574.665421862256</v>
       </c>
       <c r="I8" t="n">
-        <v>269.6019479309155</v>
+        <v>274.8948466539179</v>
       </c>
       <c r="J8" t="n">
-        <v>669.375</v>
+        <v>629.2439999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>130.4</v>
       </c>
       <c r="C9" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
-        <v>6000</v>
+        <v>6128.869811812388</v>
       </c>
       <c r="F9" t="n">
-        <v>-28.20000000000027</v>
+        <v>74.74056225943059</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>6000</v>
+        <v>6137.606748206449</v>
       </c>
       <c r="I9" t="n">
-        <v>276.5999999999996</v>
+        <v>283.1975495312566</v>
       </c>
       <c r="J9" t="n">
-        <v>671.7760000000001</v>
+        <v>687.456</v>
       </c>
       <c r="K9" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>138.8</v>
       </c>
       <c r="C10" t="n">
-        <v>23.4</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="E10" t="n">
-        <v>6085.590991343228</v>
+        <v>5642.463423900685</v>
       </c>
       <c r="F10" t="n">
-        <v>64.20484664470177</v>
+        <v>-247.120853224541</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>6091.443366819688</v>
+        <v>5574.531474441816</v>
       </c>
       <c r="I10" t="n">
-        <v>273.7231267571602</v>
+        <v>275.9261846627965</v>
       </c>
       <c r="J10" t="n">
-        <v>687.456</v>
+        <v>629.2439999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>92.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>121.4</v>
+        <v>129</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>5867.830397786607</v>
+        <v>6131.807807678029</v>
       </c>
       <c r="F11" t="n">
-        <v>-89.39934785777359</v>
+        <v>144.8390200191666</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>5851.309197509933</v>
+        <v>6137.209767009096</v>
       </c>
       <c r="I11" t="n">
-        <v>274.4257336600047</v>
+        <v>273.7258651019193</v>
       </c>
       <c r="J11" t="n">
-        <v>655.9</v>
+        <v>695.1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
